--- a/human_validation/judge/kor/judge_D015_S003_P001__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D015_S003_P001__qwen3-235b_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,187 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 오셨는지 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제가 정말 많이 느려졌기 때문에 왔어요. 회사에서는 같은 감사 작업 서류를 20분 동안 쳐다보고 있다가야 겨우 손을 움직여서 뭔가를 타이핑하기 시작해요. 사람들이 제가 따라가지 못하고 있다는 걸 눈치채기 시작했고, 이제 숨기기가 힘들어지고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 취미, 업무, 사회적 교류처럼 평소 즐거움을 느끼시던 활동에 대한 흥미나 즐거움이 줄어든 걸 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 네. 예전엔 등산 계획도 세우고, 사진도 찍고, 일요일마다 요리도 하고, 도서관 자원봉사도 했어요. 지금은 그게 다 그냥 해야 할 일 목록처럼 느껴져요, 시작할 만큼 신경도 안 쓰이고요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 최근에 식욕이나 체중에 변화가 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네. 요즘엔 별로 배가 고프지 않아요. 음식은 대부분 그냥 먹어야 한다는 걸 알아서 억지로 먹는 것 정도예요. 그리고 제 출근용 치마가 헐렁해지는 걸 느꼈는데, 일부러 살을 빼려는 건 아니었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 움직임이나 말투가 평소보다 느려지거나 더 초조해지신 걸 느끼신 적이 있나요? 예를 들어, 주변에서 느리게 움직인다거나 이유 없이 안절부절못하는 것 같다고 말한 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네. 정말 많이 느려진 느낌이에요. 회사에서는 같은 감사 작업 서류를 20분 동안 쳐다보고 있다가야 겨우 손을 움직여서 타이핑을 시작해요. 사람들이 제가 예전만큼 따라가지 못하고 있다는 걸 알아차리기 시작했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 자신이 부족하다고 느끼거나 평소보다 더 스스로를 탓하는 느낌이 드셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네. 저는 완전히 실패했다는 느낌이 들어요, 특히 돈이랑 일에 관해서요. 남편이 통장 잔고를 보여주면서 우리 괜찮다고 말해줘도, 여전히 제가 이미 우리를 재정적으로 파탄냈다는 확신이 들어요. 그리고 매니저가 제 자리는 안전하다고 말해줘도, 회사가 제가 무능하다는 증거를 조용히 모으고 있다는 생각을 멈출 수가 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 자해하고 싶다거나 삶이 살 가치가 없다는 생각을 하신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 저... 어떻게 대답해야 할지 잘 모르겠어요. 딱히 말씀드릴 만한 특별한 건 없는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 이렇게 느려지고, 흥미를 잃고, 실패했다는 느낌을 예전에도 느끼신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 잘 모르겠어요. 이번과 똑같이 느껴진 시기는 딱히 떠오르지 않아요. 예전에도 스트레스 받는 시기는 있었을지 모르지만, 이렇게 느려지거나 이렇게 막막했던 적은 없었던 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 과거에 이렇게 느려지거나, 흥미를 잃거나, 실패했다는 느낌이 하루 이틀 이상 지속됐던 시기가 있었는지 떠올려 보실 수 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 그런 시기는 딱히 기억이 안 나요. 안 좋은 날이나 스트레스 받는 시기는 있었지만, 이번처럼 지속되고 이런 느낌이었던 다른 시기가 있었다고는 말 못 하겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>진단명: 정신병적 양상을 동반한 주요우울장애 (D015)
 인구통계: 성별 여성 / 나이 32 / 직업상태 accountant or auditor / 최종학력 학사
@@ -575,245 +747,41 @@
 증상 지속 기간: None
 추가 요건: delusions_and_hallucinations occur exclusively during the major depressive episode
 주호소 증상 코드: S028
-배경 서술: 캐런의 남편이 회사 구조조정으로 인해 갑자기 가정 밖에서의 일을 그만두면서, 가계 예산과 건강보험 서류 업무가 그녀에게 무겁게 떨어졌고, 마침 회계감사 시즌과 공인회계사 시험 마감이 겹쳐 있던 시기였다. 그 후 7개월 동안, 평소 그녀의 정확함은 지속적인 낮은 기분, 등산·사진·요리·도서관 자원봉사에 대한 흥미 저하, 식욕 변화, 피로감, 업무 속도 저하로 가려졌고, 그녀는 전에 한 번도 놓친 적 없던 검토 마감을 놓치게 되었다. 삽화가 악화되면서, 남편과 상사의 안심시키는 말에도 불구하고 그녀는 재정 파탄과 직업적 불명예에 대한 고정된 믿음을 갖게 되었고, 스프레드시트나 이메일을 여는 것조차 두려워하게 만드는 생생한 지각 유사 경험을 겪기 시작했다. 그녀는 회사의 직원 지원 프로그램을 통해 정신과 진료를 받게 되었는데, 감사 담당 매니저가 지속적인 기능 저하를 알아차린 후였고, 캐런도 마지못해 일반적인 휴식과 안심시켜주는 말만으로는 더 이상 충분하지 않다는 데 동의했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 오셨는지 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제가 정말 많이 느려졌기 때문에 왔어요. 회사에서는 같은 감사 작업 서류를 20분 동안 쳐다보고 있다가야 겨우 손을 움직여서 뭔가를 타이핑하기 시작해요. 사람들이 제가 따라가지 못하고 있다는 걸 눈치채기 시작했고, 이제 숨기기가 힘들어지고 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 취미, 업무, 사회적 교류처럼 평소 즐거움을 느끼시던 활동에 대한 흥미나 즐거움이 줄어든 걸 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 네. 예전엔 등산 계획도 세우고, 사진도 찍고, 일요일마다 요리도 하고, 도서관 자원봉사도 했어요. 지금은 그게 다 그냥 해야 할 일 목록처럼 느껴져요, 시작할 만큼 신경도 안 쓰이고요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 최근에 식욕이나 체중에 변화가 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네. 요즘엔 별로 배가 고프지 않아요. 음식은 대부분 그냥 먹어야 한다는 걸 알아서 억지로 먹는 것 정도예요. 그리고 제 출근용 치마가 헐렁해지는 걸 느꼈는데, 일부러 살을 빼려는 건 아니었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 움직임이나 말투가 평소보다 느려지거나 더 초조해지신 걸 느끼신 적이 있나요? 예를 들어, 주변에서 느리게 움직인다거나 이유 없이 안절부절못하는 것 같다고 말한 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네. 정말 많이 느려진 느낌이에요. 회사에서는 같은 감사 작업 서류를 20분 동안 쳐다보고 있다가야 겨우 손을 움직여서 타이핑을 시작해요. 사람들이 제가 예전만큼 따라가지 못하고 있다는 걸 알아차리기 시작했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 자신이 부족하다고 느끼거나 평소보다 더 스스로를 탓하는 느낌이 드셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네. 저는 완전히 실패했다는 느낌이 들어요, 특히 돈이랑 일에 관해서요. 남편이 통장 잔고를 보여주면서 우리 괜찮다고 말해줘도, 여전히 제가 이미 우리를 재정적으로 파탄냈다는 확신이 들어요. 그리고 매니저가 제 자리는 안전하다고 말해줘도, 회사가 제가 무능하다는 증거를 조용히 모으고 있다는 생각을 멈출 수가 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 자해하고 싶다거나 삶이 살 가치가 없다는 생각을 하신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 저... 어떻게 대답해야 할지 잘 모르겠어요. 딱히 말씀드릴 만한 특별한 건 없는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 이렇게 느려지고, 흥미를 잃고, 실패했다는 느낌을 예전에도 느끼신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 잘 모르겠어요. 이번과 똑같이 느껴진 시기는 딱히 떠오르지 않아요. 예전에도 스트레스 받는 시기는 있었을지 모르지만, 이렇게 느려지거나 이렇게 막막했던 적은 없었던 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 과거에 이렇게 느려지거나, 흥미를 잃거나, 실패했다는 느낌이 하루 이틀 이상 지속됐던 시기가 있었는지 떠올려 보실 수 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 그런 시기는 딱히 기억이 안 나요. 안 좋은 날이나 스트레스 받는 시기는 있었지만, 이번처럼 지속되고 이런 느낌이었던 다른 시기가 있었다고는 말 못 하겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
+배경 서술: 캐런의 남편이 회사 구조조정으로 인해 갑자기 가정 밖에서의 일을 그만두면서, 가계 예산과 건강보험 서류 업무가 그녀에게 무겁게 떨어졌고, 마침 회계감사 시즌과 공인회계사 시험 마감이 겹쳐 있던 시기였다. 그 후 7개월 동안, 평소 그녀의 정확함은 지속적인 낮은 기분, 등산·사진·요리·도서관 자원봉사에 대한 흥미 저하, 식욕 변화, 피로감, 업무 속도 저하로 가려졌고, 그녀는 전에 한 번도 놓친 적 없던 검토 마감을 놓치게 되었다. 삽화가 악화되면서, 남편과 상사의 안심시키는 말에도 불구하고 그녀는 재정 파탄과 직업적 불명예에 대한 고정된 믿음을 갖게 되었고, 스프레드시트나 이메일을 여는 것조차 두려워하게 만드는 생생한 지각 유사 경험을 겪기 시작했다. 그녀는 회사의 직원 지원 프로그램을 통해 정신과 진료를 받게 되었는데, 감사 담당 매니저가 지속적인 기능 저하를 알아차린 후였고, 캐런도 마지못해 일반적인 휴식과 안심시켜주는 말만으로는 더 이상 충분하지 않다는 데 동의했다.
+표집된 증상 목록:
+  - S019 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - S020 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
+  - S024 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - S025 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - S026 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - S028 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.
+  - S029 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.</t>
+        </is>
+      </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>[8번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32.2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=4, 커버리지=0.8)
-  확인된 근거: 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
-  누락: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
-  확인된 근거: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
-  누락: 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.</t>
+          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32.2)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: 없음
+체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=4, 커버리지=0.8)
+확인된 근거:
+  - 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.
+  - 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
+확인된 근거:
+  - 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A40:B40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D015_S003_P001__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D015_S003_P001__qwen3-235b_kor.xlsx
@@ -733,6 +733,11 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -777,11 +782,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A40:B40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D015_S003_P001__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D015_S003_P001__qwen3-235b_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.1027</v>
+        <v>0.08749999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.875</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.1067</v>
+        <v>0.0979</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.5476</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.25</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
